--- a/Sajjad data/by_country_and_state/USA/IN.xlsx
+++ b/Sajjad data/by_country_and_state/USA/IN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="172">
   <si>
     <t>Business Name</t>
   </si>
@@ -326,6 +326,207 @@
   </si>
   <si>
     <t>2026-10-25T16:29:48.166Z</t>
+  </si>
+  <si>
+    <t>Fort Wayne Urgent Dentist</t>
+  </si>
+  <si>
+    <t>(260) 238-3229</t>
+  </si>
+  <si>
+    <t>2303 N Clinton St, Fort Wayne, IN 46805</t>
+  </si>
+  <si>
+    <t>Fort Wayne</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Fort+Wayne+Urgent+Dentist/data=!4m7!3m6!1s0x8815e5c89c2bba85:0xaf3fe79ce6d0157e!8m2!3d41.0964903!4d-85.1399889!16s%2Fg%2F11qg9flgnr!19sChIJhbornMjlFYgRfhXQ5pznP68?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:45:57.958Z</t>
+  </si>
+  <si>
+    <t>Swift Emergency Dental Solutions</t>
+  </si>
+  <si>
+    <t>(260) 345-0192</t>
+  </si>
+  <si>
+    <t>2122 S Calhoun St, Fort Wayne, IN 46802</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Swift+Emergency+Dental+Solutions/data=!4m7!3m6!1s0x8815e58475424949:0x93c9664c37d2b871!8m2!3d41.0655981!4d-85.1383952!16s%2Fg%2F11l770b6h2!19sChIJSUlCdYTlFYgRcbjSN0xmyZM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:46:01.969Z</t>
+  </si>
+  <si>
+    <t>Summit City Smiles, Inc.</t>
+  </si>
+  <si>
+    <t>(260) 484-5614</t>
+  </si>
+  <si>
+    <t>1330 E State Blvd, Fort Wayne, IN 46805</t>
+  </si>
+  <si>
+    <t>2.8</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Summit+City+Smiles,+Inc./data=!4m7!3m6!1s0x8815e4a745bc8d69:0xaa1249046ccb3abd!8m2!3d41.0966035!4d-85.1212206!16s%2Fg%2F1tgqk0b4!19sChIJaY28RafkFYgRvTrLbARJEqo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:46:04.013Z</t>
+  </si>
+  <si>
+    <t>Dental</t>
+  </si>
+  <si>
+    <t>(260) 338-2643</t>
+  </si>
+  <si>
+    <t>2121 E Dupont Rd, Fort Wayne, IN 46825</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental/data=!4m7!3m6!1s0x881608028cce1999:0x5ed4cfb7b82ecfbb!8m2!3d41.1795928!4d-85.1144739!16s%2Fg%2F1263ws_vs!19sChIJmRnOjAIIFogRu88uuLfP1F4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:46:07.434Z</t>
+  </si>
+  <si>
+    <t>New York Dentists Inc</t>
+  </si>
+  <si>
+    <t>(260) 423-2521</t>
+  </si>
+  <si>
+    <t>122 W Washington Blvd, Fort Wayne, IN 46802</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/New+York+Dentists+Inc/data=!4m7!3m6!1s0x8815e4f2df31ba5b:0xd0afa2329351d8fd!8m2!3d41.0772206!4d-85.1400397!16s%2Fg%2F1pv5tll63!19sChIJW7ox3_LkFYgR_dhRkzKir9A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:46:09.457Z</t>
+  </si>
+  <si>
+    <t>Fort Wayne Smiles</t>
+  </si>
+  <si>
+    <t>(260) 426-1086</t>
+  </si>
+  <si>
+    <t>2031 Reed Rd, Fort Wayne, IN 46815</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Fort+Wayne+Smiles/data=!4m7!3m6!1s0x8815fc9dec41e971:0x6f8ce32fafb4b4a3!8m2!3d41.096054!4d-85.0800702!16s%2Fg%2F1ttdz191!19sChIJcelB7J38FYgRo7S0ry_jjG8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:46:12.537Z</t>
+  </si>
+  <si>
+    <t>Yoder/Rahrig Family Dentistry</t>
+  </si>
+  <si>
+    <t>(260) 447-1776</t>
+  </si>
+  <si>
+    <t>333 E Tillman Rd, Fort Wayne, IN 46816</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Yoder%2FRahrig+Family+Dentistry/data=!4m7!3m6!1s0x8815ef883cee3e29:0x4ee5e60c4e0c40fd!8m2!3d41.0175638!4d-85.1314598!16s%2Fg%2F1tgj9f9f!19sChIJKT7uPIjvFYgR_UAMTgzm5U4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:47:47.189Z</t>
+  </si>
+  <si>
+    <t>Orthodontic Specialty Services - Dr. Aron Dellinger DDS, MSD, ABO-Board Certified</t>
+  </si>
+  <si>
+    <t>(260) 497-0497</t>
+  </si>
+  <si>
+    <t>Orthodontist</t>
+  </si>
+  <si>
+    <t>1120 E Dupont Rd, Fort Wayne, IN 46825</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Orthodontic+Specialty+Services+-+Dr.+Aron+Dellinger+DDS,+MSD,+ABO-Board+Certified/data=!4m7!3m6!1s0x8815e2a000e784db:0xe4ca8cf77894d52!8m2!3d41.1779691!4d-85.1268246!16s%2Fg%2F1td26120!19sChIJ24TnAKDiFYgRUk2Jd8-oTA4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:48:32.968Z</t>
+  </si>
+  <si>
+    <t>Dr. Timothy J. Bussick, DDS MS</t>
+  </si>
+  <si>
+    <t>(260) 436-2255</t>
+  </si>
+  <si>
+    <t>7207 Engle Rd, Fort Wayne, IN 46804</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Timothy+J.+Bussick,+DDS+MS/data=!4m7!3m6!1s0x8815e7b5914fbccb:0xf13bc9b49d600add!8m2!3d41.0427543!4d-85.2345405!16s%2Fg%2F1tfcjc6_!19sChIJy7xPkbXnFYgR3QpgnbTJO_E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:48:34.785Z</t>
+  </si>
+  <si>
+    <t>One Dental Service</t>
+  </si>
+  <si>
+    <t>(862) 872-7229</t>
+  </si>
+  <si>
+    <t>616 E Lewis St, Fort Wayne, IN 46802</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/One+Dental+Service/data=!4m7!3m6!1s0x8815e5b697027d37:0xc1f1c3abc8d4a579!8m2!3d41.0749!4d-85.1294196!16s%2Fg%2F11y3737qlv!19sChIJN30Cl7blFYgReaXUyKvD8cE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:49:28.056Z</t>
+  </si>
+  <si>
+    <t>Clinkenbeard Dentistry.</t>
+  </si>
+  <si>
+    <t>(260) 424-6031</t>
+  </si>
+  <si>
+    <t>3615 Lake Ave, Fort Wayne, IN 46805</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clinkenbeard+Dentistry./data=!4m7!3m6!1s0x8815fb5bdbb1c1d9:0xf26f95560d32bded!8m2!3d41.0904383!4d-85.092676!16s%2Fg%2F11fnyp8l5h!19sChIJ2cGx21v7FYgR7b0yDVaVb_I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:49:30.300Z</t>
+  </si>
+  <si>
+    <t>Bright White Smiles</t>
+  </si>
+  <si>
+    <t>(260) 202-2033</t>
+  </si>
+  <si>
+    <t>Teeth whitening service</t>
+  </si>
+  <si>
+    <t>5900 W Jefferson Blvd, Fort Wayne, IN 46804</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bright+White+Smiles/data=!4m7!3m6!1s0x8815e7e7e36e38a3:0xecd476a789c7a660!8m2!3d41.0613359!4d-85.2163987!16s%2Fg%2F11rfbz4hn8!19sChIJozhu4-fnFYgRYKbHiad21Ow?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:50:09.939Z</t>
   </si>
 </sst>
 </file>
@@ -706,7 +907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1297,6 +1498,498 @@
         <v>104</v>
       </c>
     </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K15" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" t="s">
+        <v>110</v>
+      </c>
+      <c r="M15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16" t="s">
+        <v>108</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s">
+        <v>38</v>
+      </c>
+      <c r="I16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" t="s">
+        <v>115</v>
+      </c>
+      <c r="M16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" t="s">
+        <v>108</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s">
+        <v>120</v>
+      </c>
+      <c r="I17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" t="s">
+        <v>31</v>
+      </c>
+      <c r="K17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" t="s">
+        <v>121</v>
+      </c>
+      <c r="M17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" t="s">
+        <v>108</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s">
+        <v>126</v>
+      </c>
+      <c r="I18" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" t="s">
+        <v>127</v>
+      </c>
+      <c r="M18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I19" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" t="s">
+        <v>132</v>
+      </c>
+      <c r="M19" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>134</v>
+      </c>
+      <c r="B20" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" t="s">
+        <v>136</v>
+      </c>
+      <c r="E20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" t="s">
+        <v>39</v>
+      </c>
+      <c r="K20" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" t="s">
+        <v>137</v>
+      </c>
+      <c r="M20" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" t="s">
+        <v>141</v>
+      </c>
+      <c r="E21" t="s">
+        <v>108</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s">
+        <v>64</v>
+      </c>
+      <c r="I21" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s">
+        <v>39</v>
+      </c>
+      <c r="K21" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" t="s">
+        <v>142</v>
+      </c>
+      <c r="M21" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B22" t="s">
+        <v>145</v>
+      </c>
+      <c r="C22" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" t="s">
+        <v>147</v>
+      </c>
+      <c r="E22" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s">
+        <v>31</v>
+      </c>
+      <c r="K22" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" t="s">
+        <v>148</v>
+      </c>
+      <c r="M22" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>150</v>
+      </c>
+      <c r="B23" t="s">
+        <v>151</v>
+      </c>
+      <c r="C23" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" t="s">
+        <v>152</v>
+      </c>
+      <c r="E23" t="s">
+        <v>108</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s">
+        <v>38</v>
+      </c>
+      <c r="I23" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" t="s">
+        <v>31</v>
+      </c>
+      <c r="K23" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" t="s">
+        <v>153</v>
+      </c>
+      <c r="M23" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>155</v>
+      </c>
+      <c r="B24" t="s">
+        <v>156</v>
+      </c>
+      <c r="C24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" t="s">
+        <v>157</v>
+      </c>
+      <c r="E24" t="s">
+        <v>108</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s">
+        <v>39</v>
+      </c>
+      <c r="I24" t="s">
+        <v>83</v>
+      </c>
+      <c r="J24" t="s">
+        <v>39</v>
+      </c>
+      <c r="K24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" t="s">
+        <v>158</v>
+      </c>
+      <c r="M24" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>160</v>
+      </c>
+      <c r="B25" t="s">
+        <v>161</v>
+      </c>
+      <c r="C25" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" t="s">
+        <v>162</v>
+      </c>
+      <c r="E25" t="s">
+        <v>108</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s">
+        <v>163</v>
+      </c>
+      <c r="I25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s">
+        <v>31</v>
+      </c>
+      <c r="K25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" t="s">
+        <v>164</v>
+      </c>
+      <c r="M25" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>166</v>
+      </c>
+      <c r="B26" t="s">
+        <v>167</v>
+      </c>
+      <c r="C26" t="s">
+        <v>168</v>
+      </c>
+      <c r="D26" t="s">
+        <v>169</v>
+      </c>
+      <c r="E26" t="s">
+        <v>108</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s">
+        <v>38</v>
+      </c>
+      <c r="I26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s">
+        <v>31</v>
+      </c>
+      <c r="K26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" t="s">
+        <v>170</v>
+      </c>
+      <c r="M26" t="s">
+        <v>171</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
